--- a/CodeSystem-feedback-payload.xlsx
+++ b/CodeSystem-feedback-payload.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -165,10 +165,10 @@
     <t>Drug Received? (yes|no)</t>
   </si>
   <si>
-    <t>Asessment</t>
-  </si>
-  <si>
-    <t>Asessment? (0|1|2|3|4|5)</t>
+    <t>assessment</t>
+  </si>
+  <si>
+    <t>assessment? (0|1|2|3|4|5)</t>
   </si>
 </sst>
 </file>

--- a/CodeSystem-feedback-payload.xlsx
+++ b/CodeSystem-feedback-payload.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-feedback-payload.xlsx
+++ b/CodeSystem-feedback-payload.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
